--- a/benchmark_cnn_hpc_metricas.xlsx
+++ b/benchmark_cnn_hpc_metricas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andym\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andym\CLASES\SEMESTRE 9\COMPUTACION DE ALTO RENDIMIENTO\CNN-optimization-with-HPC-tools-\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39FA1A4-C90E-4B0A-A4ED-1A041E203122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -16,41 +16,6 @@
     <sheet name="Benchmark CNN HPC" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Benchmark CNN HPC'!$A$2:$B$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Benchmark CNN HPC'!$C$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Benchmark CNN HPC'!$G$2:$G$13</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Benchmark CNN HPC'!$H$1</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Benchmark CNN HPC'!$H$2:$H$13</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Benchmark CNN HPC'!$I$1</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'Benchmark CNN HPC'!$I$2:$I$13</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'Benchmark CNN HPC'!$J$1</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Benchmark CNN HPC'!$J$2:$J$13</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Benchmark CNN HPC'!$K$1</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Benchmark CNN HPC'!$K$2:$K$13</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Benchmark CNN HPC'!$L$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Benchmark CNN HPC'!$C$2:$C$13</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'Benchmark CNN HPC'!$L$2:$L$13</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'Benchmark CNN HPC'!$M$1</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'Benchmark CNN HPC'!$M$2:$M$13</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'Benchmark CNN HPC'!$N$1</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'Benchmark CNN HPC'!$N$2:$N$13</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'Benchmark CNN HPC'!$O$1</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'Benchmark CNN HPC'!$O$2:$O$13</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'Benchmark CNN HPC'!$P$1</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'Benchmark CNN HPC'!$P$2:$P$13</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'Benchmark CNN HPC'!$Q$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Benchmark CNN HPC'!$D$1</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'Benchmark CNN HPC'!$Q$2:$Q$13</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'Benchmark CNN HPC'!$R$1</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'Benchmark CNN HPC'!$R$2:$R$13</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Benchmark CNN HPC'!$D$2:$D$13</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Benchmark CNN HPC'!$E$1</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Benchmark CNN HPC'!$E$2:$E$13</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Benchmark CNN HPC'!$F$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Benchmark CNN HPC'!$F$2:$F$13</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Benchmark CNN HPC'!$G$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -275,17 +240,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/benchmark_cnn_hpc_metricas.xlsx
+++ b/benchmark_cnn_hpc_metricas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andym\CLASES\SEMESTRE 9\COMPUTACION DE ALTO RENDIMIENTO\CNN-optimization-with-HPC-tools-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39FA1A4-C90E-4B0A-A4ED-1A041E203122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19682654-DCDD-4550-AB46-9EBF8E775FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark CNN HPC" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="56">
   <si>
     <t>Version</t>
   </si>
@@ -126,13 +126,76 @@
   </si>
   <si>
     <t xml:space="preserve">Python </t>
+  </si>
+  <si>
+    <t>1.03 MiB</t>
+  </si>
+  <si>
+    <t>0.31 MiB</t>
+  </si>
+  <si>
+    <t>22.98 MiB</t>
+  </si>
+  <si>
+    <t>35.59 MiB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.22 MiB</t>
+  </si>
+  <si>
+    <t>10834.829680 J</t>
+  </si>
+  <si>
+    <t>24.068641 J</t>
+  </si>
+  <si>
+    <t>2330.184716 J</t>
+  </si>
+  <si>
+    <t>233.069825 J</t>
+  </si>
+  <si>
+    <t>3310.440130 J</t>
+  </si>
+  <si>
+    <t>RAY</t>
+  </si>
+  <si>
+    <t>Memoria (Equipo local)</t>
+  </si>
+  <si>
+    <t>Energía (Patagón)</t>
+  </si>
+  <si>
+    <t>Tiempos (Patagón)</t>
+  </si>
+  <si>
+    <t>Tiempos</t>
+  </si>
+  <si>
+    <t>Equipo Local</t>
+  </si>
+  <si>
+    <t>N=500</t>
+  </si>
+  <si>
+    <t>N=1000</t>
+  </si>
+  <si>
+    <t>N=5000</t>
+  </si>
+  <si>
+    <t>N=8000</t>
+  </si>
+  <si>
+    <t>Escalabilidad (Patagón)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +213,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -171,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -220,14 +291,58 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color rgb="FF999999"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color rgb="FF999999"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
       </bottom>
       <diagonal/>
     </border>
@@ -235,22 +350,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,8 +432,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BenchmarkTable" displayName="BenchmarkTable" ref="A1:T13">
-  <autoFilter ref="A1:T13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BenchmarkTable" displayName="BenchmarkTable" ref="A2:T17">
+  <autoFilter ref="A2:T17" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Version"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Benchmark"/>
@@ -318,16 +447,24 @@
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Rep 8" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Rep 9" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Rep 10" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Promedio (s)"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Promedio (s)">
+      <calculatedColumnFormula>AVERAGE(C3:L3)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Std (s)" dataDxfId="0">
       <calculatedColumnFormula>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Min (s)"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Max (s)"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Min (s)">
+      <calculatedColumnFormula>MIN(C3:L3)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Max (s)">
+      <calculatedColumnFormula>MAX(C3:L3)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Baseline Python (s)"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Speedup"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Threads"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Eficiencia"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Eficiencia">
+      <calculatedColumnFormula>IFERROR(R3/S3,"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -618,401 +755,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="10"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C3" s="2">
         <v>52.7759</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D3" s="2">
         <v>53.934399999999997</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E3" s="2">
         <v>52.967799999999997</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F3" s="2">
         <v>52.572000000000003</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G3" s="2">
         <v>52.821599999999997</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H3" s="2">
         <v>53.421300000000002</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I3" s="2">
         <v>53.253599999999999</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J3" s="2">
         <v>52.9193</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K3" s="2">
         <v>54.165599999999998</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L3" s="2">
         <v>52.722099999999998</v>
       </c>
-      <c r="M2">
-        <f t="shared" ref="M2:M13" si="0">AVERAGE(C2:L2)</f>
+      <c r="M3">
+        <f t="shared" ref="M3:M6" si="0">AVERAGE(C3:L3)</f>
         <v>53.155359999999995</v>
       </c>
-      <c r="N2">
+      <c r="N3">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
         <v>0.50815107832218498</v>
       </c>
-      <c r="O2">
-        <f t="shared" ref="O2:O13" si="1">MIN(C2:L2)</f>
+      <c r="O3">
+        <f t="shared" ref="O3:O6" si="1">MIN(C3:L3)</f>
         <v>52.572000000000003</v>
       </c>
-      <c r="P2">
-        <f t="shared" ref="P2:P13" si="2">MAX(C2:L2)</f>
+      <c r="P3">
+        <f t="shared" ref="P3:P6" si="2">MAX(C3:L3)</f>
         <v>54.165599999999998</v>
       </c>
-      <c r="Q2">
-        <f>M2</f>
+      <c r="Q3">
+        <f>M3</f>
         <v>53.155359999999995</v>
       </c>
-      <c r="R2">
-        <f t="shared" ref="R2:R13" si="3">IFERROR(Q2/M2,"")</f>
+      <c r="R3">
+        <f t="shared" ref="R3:R6" si="3">IFERROR(Q3/M3,"")</f>
         <v>1</v>
       </c>
-      <c r="T2" t="str">
-        <f t="shared" ref="T2:T13" si="4">IFERROR(R2/S2,"")</f>
+      <c r="T3" t="str">
+        <f t="shared" ref="T3:T6" si="4">IFERROR(R3/S3,"")</f>
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C4" s="2">
         <v>7.3099999999999998E-2</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D4" s="2">
         <v>4.3700000000000003E-2</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E4" s="2">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F4" s="2">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G4" s="2">
         <v>4.9299999999999997E-2</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H4" s="2">
         <v>4.0599999999999997E-2</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I4" s="2">
         <v>6.8699999999999997E-2</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J4" s="2">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K4" s="2">
         <v>4.02E-2</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L4" s="2">
         <v>5.9900000000000002E-2</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <f t="shared" si="0"/>
         <v>5.0700000000000002E-2</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
         <v>1.1563909373563941E-2</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <f t="shared" si="1"/>
         <v>4.02E-2</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <f t="shared" si="2"/>
         <v>7.3099999999999998E-2</v>
       </c>
-      <c r="Q3">
-        <f>M2</f>
+      <c r="Q4">
+        <f>M3</f>
         <v>53.155359999999995</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <f t="shared" si="3"/>
         <v>1048.4291913214988</v>
       </c>
-      <c r="T3" t="str">
+      <c r="T4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C5" s="2">
         <v>0.14660000000000001</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D5" s="2">
         <v>0.1188</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E5" s="2">
         <v>0.12959999999999999</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F5" s="2">
         <v>0.1182</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G5" s="2">
         <v>0.1255</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H5" s="2">
         <v>0.17119999999999999</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I5" s="2">
         <v>0.14430000000000001</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J5" s="2">
         <v>0.13489999999999999</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K5" s="2">
         <v>0.12280000000000001</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L5" s="2">
         <v>0.14849999999999999</v>
       </c>
-      <c r="M4">
+      <c r="M5">
         <f t="shared" si="0"/>
         <v>0.13603999999999999</v>
       </c>
-      <c r="N4">
+      <c r="N5">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
         <v>1.5861475341215833E-2</v>
       </c>
-      <c r="O4">
+      <c r="O5">
         <f t="shared" si="1"/>
         <v>0.1182</v>
       </c>
-      <c r="P4">
+      <c r="P5">
         <f t="shared" si="2"/>
         <v>0.17119999999999999</v>
       </c>
-      <c r="Q4">
-        <f>M2</f>
+      <c r="Q5">
+        <f>M3</f>
         <v>53.155359999999995</v>
       </c>
-      <c r="R4">
+      <c r="R5">
         <f t="shared" si="3"/>
         <v>390.73331373125546</v>
       </c>
-      <c r="S4">
+      <c r="S5">
         <v>6</v>
       </c>
-      <c r="T4">
+      <c r="T5">
         <f t="shared" si="4"/>
         <v>65.122218955209249</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C6" s="2">
         <v>1.2032</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D6" s="2">
         <v>1.1868000000000001</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E6" s="2">
         <v>0.94059999999999999</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F6" s="2">
         <v>0.95330000000000004</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G6" s="2">
         <v>1.1608000000000001</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H6" s="2">
         <v>1.1836</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I6" s="2">
         <v>0.95709999999999995</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J6" s="2">
         <v>1.1329</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K6" s="2">
         <v>0.99450000000000005</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L6" s="2">
         <v>0.97650000000000003</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <f t="shared" si="0"/>
         <v>1.0689299999999999</v>
       </c>
-      <c r="N5">
+      <c r="N6">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
         <v>0.1067853927276573</v>
       </c>
-      <c r="O5">
+      <c r="O6">
         <f t="shared" si="1"/>
         <v>0.94059999999999999</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <f t="shared" si="2"/>
         <v>1.2032</v>
       </c>
-      <c r="Q5">
-        <f>M2</f>
+      <c r="Q6">
+        <f>M3</f>
         <v>53.155359999999995</v>
       </c>
-      <c r="R5">
+      <c r="R6">
         <f t="shared" si="3"/>
         <v>49.727634176232307</v>
-      </c>
-      <c r="T5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="7">
-        <v>58.154699999999998</v>
-      </c>
-      <c r="D6" s="7">
-        <v>58.182200000000002</v>
-      </c>
-      <c r="E6" s="7">
-        <v>57.320900000000002</v>
-      </c>
-      <c r="F6" s="7">
-        <v>57.659300000000002</v>
-      </c>
-      <c r="G6" s="7">
-        <v>57.891300000000001</v>
-      </c>
-      <c r="H6" s="7">
-        <v>57.954099999999997</v>
-      </c>
-      <c r="I6" s="7">
-        <v>58.2943</v>
-      </c>
-      <c r="J6" s="7">
-        <v>58.810699999999997</v>
-      </c>
-      <c r="K6" s="7">
-        <v>58.645499999999998</v>
-      </c>
-      <c r="L6" s="7">
-        <v>57.954700000000003</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>58.086770000000001</v>
-      </c>
-      <c r="N6">
-        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>0.41660337504633704</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="1"/>
-        <v>57.320900000000002</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="2"/>
-        <v>58.810699999999997</v>
-      </c>
-      <c r="Q6">
-        <f>M6</f>
-        <v>58.086770000000001</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="3"/>
-        <v>1</v>
       </c>
       <c r="T6" t="str">
         <f t="shared" si="4"/>
@@ -1021,673 +1116,1169 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.1003</v>
-      </c>
-      <c r="E7" s="7">
-        <v>9.4200000000000006E-2</v>
-      </c>
-      <c r="F7" s="7">
-        <v>9.2700000000000005E-2</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.13819999999999999</v>
-      </c>
-      <c r="H7" s="7">
-        <v>8.3400000000000002E-2</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0.1195</v>
-      </c>
-      <c r="J7" s="7">
-        <v>9.1899999999999996E-2</v>
-      </c>
-      <c r="K7" s="7">
-        <v>9.9500000000000005E-2</v>
-      </c>
-      <c r="L7" s="7">
-        <v>8.5099999999999995E-2</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="2">
+        <v>11.278700000000001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>11.4213</v>
+      </c>
+      <c r="E7" s="2">
+        <v>11.892300000000001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10.8391</v>
+      </c>
+      <c r="G7" s="2">
+        <v>11.129300000000001</v>
+      </c>
+      <c r="H7" s="2">
+        <v>11.290100000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>12.1151</v>
+      </c>
+      <c r="J7" s="2">
+        <v>11.7623</v>
+      </c>
+      <c r="K7" s="2">
+        <v>11.651199999999999</v>
+      </c>
+      <c r="L7" s="2">
+        <v>10.956200000000001</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
-        <v>9.9979999999999999E-2</v>
+        <f t="shared" ref="M7" si="5">AVERAGE(C7:L7)</f>
+        <v>11.43356</v>
       </c>
       <c r="N7">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>1.5858549744538375E-2</v>
+        <v>0.39356300944067374</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
-        <v>8.3400000000000002E-2</v>
+        <f t="shared" ref="O7" si="6">MIN(C7:L7)</f>
+        <v>10.8391</v>
       </c>
       <c r="P7">
-        <f t="shared" si="2"/>
-        <v>0.13819999999999999</v>
+        <f t="shared" ref="P7" si="7">MAX(C7:L7)</f>
+        <v>12.1151</v>
       </c>
       <c r="Q7">
-        <f>M6</f>
-        <v>58.086770000000001</v>
+        <f>M3</f>
+        <v>53.155359999999995</v>
       </c>
       <c r="R7">
-        <f t="shared" si="3"/>
-        <v>580.98389677935586</v>
+        <f>IFERROR(BenchmarkTable[[#This Row],[Baseline Python (s)]]/BenchmarkTable[[#This Row],[Promedio (s)]],"")</f>
+        <v>4.6490646832657543</v>
       </c>
       <c r="T7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="T7" si="8">IFERROR(R7/S7,"")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="7">
-        <v>6.3739999999999997</v>
-      </c>
-      <c r="D8" s="7">
-        <v>6.5787000000000004</v>
-      </c>
-      <c r="E8" s="7">
-        <v>6.4047999999999998</v>
-      </c>
-      <c r="F8" s="7">
-        <v>5.9572000000000003</v>
-      </c>
-      <c r="G8" s="7">
-        <v>6.0659000000000001</v>
-      </c>
-      <c r="H8" s="7">
-        <v>6.3003</v>
-      </c>
-      <c r="I8" s="7">
-        <v>6.3685999999999998</v>
-      </c>
-      <c r="J8" s="7">
-        <v>6.4221000000000004</v>
-      </c>
-      <c r="K8" s="7">
-        <v>6.3951000000000002</v>
-      </c>
-      <c r="L8" s="7">
-        <v>6.9234</v>
+      <c r="C8" s="2">
+        <v>58.154699999999998</v>
+      </c>
+      <c r="D8" s="2">
+        <v>58.182200000000002</v>
+      </c>
+      <c r="E8" s="2">
+        <v>57.320900000000002</v>
+      </c>
+      <c r="F8" s="2">
+        <v>57.659300000000002</v>
+      </c>
+      <c r="G8" s="2">
+        <v>57.891300000000001</v>
+      </c>
+      <c r="H8" s="2">
+        <v>57.954099999999997</v>
+      </c>
+      <c r="I8" s="2">
+        <v>58.2943</v>
+      </c>
+      <c r="J8" s="2">
+        <v>58.810699999999997</v>
+      </c>
+      <c r="K8" s="2">
+        <v>58.645499999999998</v>
+      </c>
+      <c r="L8" s="2">
+        <v>57.954700000000003</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
-        <v>6.3790100000000001</v>
+        <f>AVERAGE(C8:L8)</f>
+        <v>58.086770000000001</v>
       </c>
       <c r="N8">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>0.24926042786611755</v>
+        <v>0.41660337504633704</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
-        <v>5.9572000000000003</v>
+        <f>MIN(C8:L8)</f>
+        <v>57.320900000000002</v>
       </c>
       <c r="P8">
-        <f t="shared" si="2"/>
-        <v>6.9234</v>
+        <f>MAX(C8:L8)</f>
+        <v>58.810699999999997</v>
       </c>
       <c r="Q8">
-        <f>M6</f>
+        <f>M8</f>
         <v>58.086770000000001</v>
       </c>
       <c r="R8">
-        <f t="shared" si="3"/>
-        <v>9.1059223923461481</v>
-      </c>
-      <c r="S8">
-        <v>6</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="4"/>
-        <v>1.5176537320576913</v>
+        <f>IFERROR(Q8/M8,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T8" t="str">
+        <f>IFERROR(R8/S8,"")</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="7">
-        <v>2.0994000000000002</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.696</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2.1570999999999998</v>
-      </c>
-      <c r="F9" s="7">
-        <v>2.0413000000000001</v>
-      </c>
-      <c r="G9" s="7">
-        <v>2.0566</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1.8619000000000001</v>
-      </c>
-      <c r="I9" s="7">
-        <v>2.1099000000000001</v>
-      </c>
-      <c r="J9" s="7">
-        <v>2.4163999999999999</v>
-      </c>
-      <c r="K9" s="7">
-        <v>2.0032000000000001</v>
-      </c>
-      <c r="L9" s="7">
-        <v>2.2543000000000002</v>
+      <c r="C9" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.1003</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9.4200000000000006E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.13819999999999999</v>
+      </c>
+      <c r="H9" s="2">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.1195</v>
+      </c>
+      <c r="J9" s="2">
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="K9" s="2">
+        <v>9.9500000000000005E-2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>8.5099999999999995E-2</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
-        <v>2.0696099999999999</v>
+        <f>AVERAGE(C9:L9)</f>
+        <v>9.9979999999999999E-2</v>
       </c>
       <c r="N9">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>0.18778919271353184</v>
+        <v>1.5858549744538375E-2</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
-        <v>1.696</v>
+        <f>MIN(C9:L9)</f>
+        <v>8.3400000000000002E-2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="2"/>
-        <v>2.4163999999999999</v>
+        <f>MAX(C9:L9)</f>
+        <v>0.13819999999999999</v>
       </c>
       <c r="Q9">
-        <f>M6</f>
+        <f>M8</f>
         <v>58.086770000000001</v>
       </c>
       <c r="R9">
-        <f t="shared" si="3"/>
-        <v>28.066529442745253</v>
+        <f>IFERROR(Q9/M9,"")</f>
+        <v>580.98389677935586</v>
       </c>
       <c r="T9" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(R9/S9,"")</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="7">
-        <v>135.05680000000001</v>
-      </c>
-      <c r="D10" s="7">
-        <v>134.9118</v>
-      </c>
-      <c r="E10" s="7">
-        <v>135.43860000000001</v>
-      </c>
-      <c r="F10" s="7">
-        <v>135.5625</v>
-      </c>
-      <c r="G10" s="7">
-        <v>134.2911</v>
-      </c>
-      <c r="H10" s="7">
-        <v>133.446</v>
-      </c>
-      <c r="I10" s="7">
-        <v>133.5849</v>
-      </c>
-      <c r="J10" s="7">
-        <v>133.92830000000001</v>
-      </c>
-      <c r="K10" s="7">
-        <v>135.19300000000001</v>
-      </c>
-      <c r="L10" s="7">
-        <v>133.80889999999999</v>
+        <v>25</v>
+      </c>
+      <c r="C10" s="2">
+        <v>6.3739999999999997</v>
+      </c>
+      <c r="D10" s="2">
+        <v>6.5787000000000004</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6.4047999999999998</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5.9572000000000003</v>
+      </c>
+      <c r="G10" s="2">
+        <v>6.0659000000000001</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6.3003</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.3685999999999998</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6.4221000000000004</v>
+      </c>
+      <c r="K10" s="2">
+        <v>6.3951000000000002</v>
+      </c>
+      <c r="L10" s="2">
+        <v>6.9234</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
-        <v>134.52219000000002</v>
+        <f>AVERAGE(C10:L10)</f>
+        <v>6.3790100000000001</v>
       </c>
       <c r="N10">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>0.75902767070773092</v>
+        <v>0.24926042786611755</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
-        <v>133.446</v>
+        <f>MIN(C10:L10)</f>
+        <v>5.9572000000000003</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
-        <v>135.5625</v>
+        <f>MAX(C10:L10)</f>
+        <v>6.9234</v>
       </c>
       <c r="Q10">
-        <f>M10</f>
-        <v>134.52219000000002</v>
+        <f>M8</f>
+        <v>58.086770000000001</v>
       </c>
       <c r="R10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IFERROR(Q10/M10,"")</f>
+        <v>9.1059223923461481</v>
+      </c>
+      <c r="S10">
+        <v>6</v>
+      </c>
+      <c r="T10">
+        <f>IFERROR(R10/S10,"")</f>
+        <v>1.5176537320576913</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.3639</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0.30409999999999998</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.31530000000000002</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.30719999999999997</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0.26319999999999999</v>
-      </c>
-      <c r="H11" s="7">
-        <v>0.27229999999999999</v>
-      </c>
-      <c r="I11" s="7">
-        <v>0.26469999999999999</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0.27329999999999999</v>
-      </c>
-      <c r="K11" s="7">
-        <v>0.25069999999999998</v>
-      </c>
-      <c r="L11" s="7">
-        <v>0.2681</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2.0994000000000002</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.696</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.1570999999999998</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2.0413000000000001</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2.0566</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1.8619000000000001</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2.1099000000000001</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2.4163999999999999</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.0032000000000001</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2.2543000000000002</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
-        <v>0.28827999999999998</v>
+        <f>AVERAGE(C11:L11)</f>
+        <v>2.0696099999999999</v>
       </c>
       <c r="N11">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>3.2466869266992833E-2</v>
+        <v>0.18778919271353184</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
-        <v>0.25069999999999998</v>
+        <f>MIN(C11:L11)</f>
+        <v>1.696</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
-        <v>0.3639</v>
+        <f>MAX(C11:L11)</f>
+        <v>2.4163999999999999</v>
       </c>
       <c r="Q11">
-        <f>M10</f>
-        <v>134.52219000000002</v>
+        <f>M8</f>
+        <v>58.086770000000001</v>
       </c>
       <c r="R11">
-        <f t="shared" si="3"/>
-        <v>466.63726238379365</v>
+        <f>IFERROR(Q11/M11,"")</f>
+        <v>28.066529442745253</v>
       </c>
       <c r="T11" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(R11/S11,"")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="7">
-        <v>19.2925</v>
-      </c>
-      <c r="D12" s="7">
-        <v>18.978300000000001</v>
-      </c>
-      <c r="E12" s="7">
-        <v>19.3202</v>
-      </c>
-      <c r="F12" s="7">
-        <v>18.910499999999999</v>
-      </c>
-      <c r="G12" s="7">
-        <v>19.1464</v>
-      </c>
-      <c r="H12" s="7">
-        <v>19.418600000000001</v>
-      </c>
-      <c r="I12" s="7">
-        <v>19.092400000000001</v>
-      </c>
-      <c r="J12" s="7">
-        <v>19.247800000000002</v>
-      </c>
-      <c r="K12" s="7">
-        <v>19.2288</v>
-      </c>
-      <c r="L12" s="7">
-        <v>18.879100000000001</v>
+        <v>25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>17.065999999999999</v>
+      </c>
+      <c r="D12" s="2">
+        <v>18.2134</v>
+      </c>
+      <c r="E12" s="2">
+        <v>17.981999999999999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>16.2395</v>
+      </c>
+      <c r="G12" s="2">
+        <v>17.8994</v>
+      </c>
+      <c r="H12" s="2">
+        <v>18.941199999999998</v>
+      </c>
+      <c r="I12" s="2">
+        <v>17.999099999999999</v>
+      </c>
+      <c r="J12" s="2">
+        <v>17.0139</v>
+      </c>
+      <c r="K12" s="2">
+        <v>16.432099999999998</v>
+      </c>
+      <c r="L12" s="2">
+        <v>17.913799999999998</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
-        <v>19.15146</v>
+        <f>AVERAGE(C12:L12)</f>
+        <v>17.570039999999999</v>
       </c>
       <c r="N12">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>0.17341622876766769</v>
+        <v>0.80641406634557156</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
-        <v>18.879100000000001</v>
+        <f>MIN(C12:L12)</f>
+        <v>16.2395</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
-        <v>19.418600000000001</v>
+        <f>MAX(C12:L12)</f>
+        <v>18.941199999999998</v>
       </c>
       <c r="Q12">
-        <f>M10</f>
-        <v>134.52219000000002</v>
+        <f>M8</f>
+        <v>58.086770000000001</v>
       </c>
       <c r="R12">
-        <f t="shared" si="3"/>
-        <v>7.024121920730849</v>
-      </c>
-      <c r="S12">
-        <v>6</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="4"/>
-        <v>1.1706869867884748</v>
+        <f>IFERROR(BenchmarkTable[[#This Row],[Baseline Python (s)]]/M12,"")</f>
+        <v>3.3060123938249433</v>
+      </c>
+      <c r="T12" t="str">
+        <f>IFERROR(R12/S12,"")</f>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="7">
-        <v>11.781599999999999</v>
-      </c>
-      <c r="D13" s="7">
-        <v>11.973599999999999</v>
-      </c>
-      <c r="E13" s="7">
-        <v>11.3941</v>
-      </c>
-      <c r="F13" s="7">
-        <v>13.6982</v>
-      </c>
-      <c r="G13" s="7">
-        <v>13.9497</v>
-      </c>
-      <c r="H13" s="7">
-        <v>13.5623</v>
-      </c>
-      <c r="I13" s="7">
-        <v>11.6541</v>
-      </c>
-      <c r="J13" s="7">
-        <v>11.615</v>
-      </c>
-      <c r="K13" s="7">
-        <v>13.345800000000001</v>
-      </c>
-      <c r="L13" s="7">
-        <v>13.920299999999999</v>
+      <c r="C13" s="2">
+        <v>135.05680000000001</v>
+      </c>
+      <c r="D13" s="2">
+        <v>134.9118</v>
+      </c>
+      <c r="E13" s="2">
+        <v>135.43860000000001</v>
+      </c>
+      <c r="F13" s="2">
+        <v>135.5625</v>
+      </c>
+      <c r="G13" s="2">
+        <v>134.2911</v>
+      </c>
+      <c r="H13" s="2">
+        <v>133.446</v>
+      </c>
+      <c r="I13" s="2">
+        <v>133.5849</v>
+      </c>
+      <c r="J13" s="2">
+        <v>133.92830000000001</v>
+      </c>
+      <c r="K13" s="2">
+        <v>135.19300000000001</v>
+      </c>
+      <c r="L13" s="2">
+        <v>133.80889999999999</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
-        <v>12.689469999999998</v>
+        <f>AVERAGE(C13:L13)</f>
+        <v>134.52219000000002</v>
       </c>
       <c r="N13">
         <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
+        <v>0.75902767070773092</v>
+      </c>
+      <c r="O13">
+        <f>MIN(C13:L13)</f>
+        <v>133.446</v>
+      </c>
+      <c r="P13">
+        <f>MAX(C13:L13)</f>
+        <v>135.5625</v>
+      </c>
+      <c r="Q13">
+        <f>M13</f>
+        <v>134.52219000000002</v>
+      </c>
+      <c r="R13">
+        <f>IFERROR(Q13/M13,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T13" t="str">
+        <f>IFERROR(R13/S13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.3639</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.30409999999999998</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.31530000000000002</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.30719999999999997</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.26319999999999999</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.27229999999999999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.26469999999999999</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.27329999999999999</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.25069999999999998</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.2681</v>
+      </c>
+      <c r="M14">
+        <f>AVERAGE(C14:L14)</f>
+        <v>0.28827999999999998</v>
+      </c>
+      <c r="N14">
+        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
+        <v>3.2466869266992833E-2</v>
+      </c>
+      <c r="O14">
+        <f>MIN(C14:L14)</f>
+        <v>0.25069999999999998</v>
+      </c>
+      <c r="P14">
+        <f>MAX(C14:L14)</f>
+        <v>0.3639</v>
+      </c>
+      <c r="Q14">
+        <f>M13</f>
+        <v>134.52219000000002</v>
+      </c>
+      <c r="R14">
+        <f>IFERROR(Q14/M14,"")</f>
+        <v>466.63726238379365</v>
+      </c>
+      <c r="T14" t="str">
+        <f>IFERROR(R14/S14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2">
+        <v>19.2925</v>
+      </c>
+      <c r="D15" s="2">
+        <v>18.978300000000001</v>
+      </c>
+      <c r="E15" s="2">
+        <v>19.3202</v>
+      </c>
+      <c r="F15" s="2">
+        <v>18.910499999999999</v>
+      </c>
+      <c r="G15" s="2">
+        <v>19.1464</v>
+      </c>
+      <c r="H15" s="2">
+        <v>19.418600000000001</v>
+      </c>
+      <c r="I15" s="2">
+        <v>19.092400000000001</v>
+      </c>
+      <c r="J15" s="2">
+        <v>19.247800000000002</v>
+      </c>
+      <c r="K15" s="2">
+        <v>19.2288</v>
+      </c>
+      <c r="L15" s="2">
+        <v>18.879100000000001</v>
+      </c>
+      <c r="M15">
+        <f>AVERAGE(C15:L15)</f>
+        <v>19.15146</v>
+      </c>
+      <c r="N15">
+        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
+        <v>0.17341622876766769</v>
+      </c>
+      <c r="O15">
+        <f>MIN(C15:L15)</f>
+        <v>18.879100000000001</v>
+      </c>
+      <c r="P15">
+        <f>MAX(C15:L15)</f>
+        <v>19.418600000000001</v>
+      </c>
+      <c r="Q15">
+        <f>M13</f>
+        <v>134.52219000000002</v>
+      </c>
+      <c r="R15">
+        <f>IFERROR(Q15/M15,"")</f>
+        <v>7.024121920730849</v>
+      </c>
+      <c r="S15">
+        <v>6</v>
+      </c>
+      <c r="T15">
+        <f>IFERROR(R15/S15,"")</f>
+        <v>1.1706869867884748</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2">
+        <v>11.781599999999999</v>
+      </c>
+      <c r="D16" s="2">
+        <v>11.973599999999999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>11.3941</v>
+      </c>
+      <c r="F16" s="2">
+        <v>13.6982</v>
+      </c>
+      <c r="G16" s="2">
+        <v>13.9497</v>
+      </c>
+      <c r="H16" s="2">
+        <v>13.5623</v>
+      </c>
+      <c r="I16" s="2">
+        <v>11.6541</v>
+      </c>
+      <c r="J16" s="2">
+        <v>11.615</v>
+      </c>
+      <c r="K16" s="2">
+        <v>13.345800000000001</v>
+      </c>
+      <c r="L16" s="2">
+        <v>13.920299999999999</v>
+      </c>
+      <c r="M16">
+        <f>AVERAGE(C16:L16)</f>
+        <v>12.689469999999998</v>
+      </c>
+      <c r="N16">
+        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
         <v>1.0273469560474691</v>
       </c>
-      <c r="O13">
-        <f t="shared" si="1"/>
+      <c r="O16">
+        <f>MIN(C16:L16)</f>
         <v>11.3941</v>
       </c>
-      <c r="P13">
-        <f t="shared" si="2"/>
+      <c r="P16">
+        <f>MAX(C16:L16)</f>
         <v>13.9497</v>
       </c>
-      <c r="Q13">
-        <f>M10</f>
+      <c r="Q16">
+        <f>M13</f>
         <v>134.52219000000002</v>
       </c>
-      <c r="R13">
-        <f t="shared" si="3"/>
+      <c r="R16">
+        <f>IFERROR(Q16/M16,"")</f>
         <v>10.601088146313442</v>
       </c>
-      <c r="T13" t="str">
-        <f t="shared" si="4"/>
+      <c r="T16" t="str">
+        <f>IFERROR(R16/S16,"")</f>
         <v/>
       </c>
     </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>40.53</v>
+      </c>
+      <c r="D17">
+        <v>41.853999999999999</v>
+      </c>
+      <c r="E17">
+        <v>40.909999999999997</v>
+      </c>
+      <c r="F17">
+        <v>42.03</v>
+      </c>
+      <c r="G17">
+        <v>41.4</v>
+      </c>
+      <c r="H17">
+        <v>40.21</v>
+      </c>
+      <c r="I17">
+        <v>41.14</v>
+      </c>
+      <c r="J17">
+        <v>42.44</v>
+      </c>
+      <c r="K17">
+        <v>40.61</v>
+      </c>
+      <c r="L17">
+        <v>41.02</v>
+      </c>
+      <c r="M17">
+        <f t="shared" ref="M17" si="9">AVERAGE(C17:L17)</f>
+        <v>41.214399999999998</v>
+      </c>
+      <c r="N17">
+        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
+        <v>0.67744685400406079</v>
+      </c>
+      <c r="O17">
+        <f t="shared" ref="O17" si="10">MIN(C17:L17)</f>
+        <v>40.21</v>
+      </c>
+      <c r="P17">
+        <f t="shared" ref="P17" si="11">MAX(C17:L17)</f>
+        <v>42.44</v>
+      </c>
+      <c r="Q17">
+        <f>M13</f>
+        <v>134.52219000000002</v>
+      </c>
+      <c r="R17">
+        <f t="shared" ref="R17" si="12">IFERROR(Q17/M17,"")</f>
+        <v>3.2639608971621579</v>
+      </c>
+      <c r="T17" t="str">
+        <f t="shared" ref="T17" si="13">IFERROR(R17/S17,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="F20" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="7">
+        <v>34.920999999999999</v>
+      </c>
+      <c r="D22" s="7">
+        <f>IFERROR(C22/C22,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="7">
+        <v>94.712800000000001</v>
+      </c>
+      <c r="H22" s="7">
+        <v>190.83959999999999</v>
+      </c>
+      <c r="I22" s="7">
+        <v>941.89610000000005</v>
+      </c>
+      <c r="J22" s="7">
+        <v>1491.5953</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="8">
+        <v>4.36E-2</v>
+      </c>
+      <c r="D23" s="8">
+        <f>IFERROR(C22/C23,"")</f>
+        <v>800.94036697247702</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0.1978</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0.52070000000000005</v>
+      </c>
+      <c r="I23" s="8">
+        <v>2.2143000000000002</v>
+      </c>
+      <c r="J23" s="8">
+        <v>3.1835</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="D24" s="7">
+        <f>IFERROR(C22/C24,"")</f>
+        <v>718.53909465020581</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="7">
+        <v>20.008400000000002</v>
+      </c>
+      <c r="H24" s="7">
+        <v>39.736600000000003</v>
+      </c>
+      <c r="I24" s="7">
+        <v>203.23910000000001</v>
+      </c>
+      <c r="J24" s="7">
+        <v>314.22109999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0.11559999999999999</v>
+      </c>
+      <c r="D25" s="8">
+        <f>IFERROR(C22/C25,"")</f>
+        <v>302.0847750865052</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="8">
+        <v>2.4047999999999998</v>
+      </c>
+      <c r="H25" s="8">
+        <v>3.2244999999999999</v>
+      </c>
+      <c r="I25" s="8">
+        <v>13.637700000000001</v>
+      </c>
+      <c r="J25" s="8">
+        <v>19.771599999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="7">
+        <v>4.5210999999999997</v>
+      </c>
+      <c r="D26" s="7">
+        <f>IFERROR(C22/C26,"")</f>
+        <v>7.7240052199685918</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="6">
+        <v>28.4453</v>
+      </c>
+      <c r="H26" s="6">
+        <v>56.511299999999999</v>
+      </c>
+      <c r="I26" s="6">
+        <v>278.31009999999998</v>
+      </c>
+      <c r="J26" s="6">
+        <v>440.82389999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="8">
+        <v>38.875100000000003</v>
+      </c>
+      <c r="D27" s="8">
+        <f>IFERROR(C27/C27,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="7">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="D28" s="7">
+        <f>IFERROR(C27/C28,"")</f>
+        <v>603.65062111801251</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="8">
+        <v>7.7088000000000001</v>
+      </c>
+      <c r="D29" s="8">
+        <f>IFERROR(C27/C29,"")</f>
+        <v>5.0429509132420094</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="I29" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.31790000000000002</v>
+      </c>
+      <c r="D30" s="7">
+        <f>IFERROR(C27/C30,"")</f>
+        <v>122.28719723183391</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="8">
+        <v>12.2097</v>
+      </c>
+      <c r="D31" s="8">
+        <f>IFERROR(C27/C31,"")</f>
+        <v>3.1839521036552907</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="9">
-        <v>18.8398</v>
-      </c>
-      <c r="D20" s="9">
-        <v>18.626000000000001</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="3">
-        <f t="shared" ref="M20:M23" si="5">AVERAGE(C20:L20)</f>
-        <v>18.732900000000001</v>
-      </c>
-      <c r="N20" s="3" t="e">
-        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O20" s="3">
-        <f t="shared" ref="O20:O23" si="6">MIN(C20:L20)</f>
-        <v>18.626000000000001</v>
-      </c>
-      <c r="P20" s="3">
-        <f t="shared" ref="P20:P23" si="7">MAX(C20:L20)</f>
-        <v>18.8398</v>
-      </c>
-      <c r="Q20" s="3">
-        <f>M20</f>
-        <v>18.732900000000001</v>
-      </c>
-      <c r="R20" s="3">
-        <f t="shared" ref="R20:R23" si="8">IFERROR(Q20/M20,"")</f>
+      <c r="C32" s="7">
+        <v>94.712800000000001</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" ref="D32" si="14">IFERROR(C32/C32,"")</f>
         <v>1</v>
       </c>
-      <c r="S20" s="3">
-        <v>1</v>
-      </c>
-      <c r="T20" s="5">
-        <f t="shared" ref="T20:T23" si="9">IFERROR(R20/S20,"")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="F32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.1978</v>
+      </c>
+      <c r="D33" s="8">
+        <f>IFERROR(C32/C33,"")</f>
+        <v>478.83114256825075</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="G33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="4" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N21" s="4" t="e">
-        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O21" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4">
-        <f>M20</f>
-        <v>18.732900000000001</v>
-      </c>
-      <c r="R21" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="S21" s="4">
-        <v>2</v>
-      </c>
-      <c r="T21" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="C34" s="7">
+        <v>20.008400000000002</v>
+      </c>
+      <c r="D34" s="7">
+        <f>IFERROR(C32/C34,"")</f>
+        <v>4.7336518662161886</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="3" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N22" s="3" t="e">
-        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O22" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <f>M20</f>
-        <v>18.732900000000001</v>
-      </c>
-      <c r="R22" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="S22" s="3">
-        <v>4</v>
-      </c>
-      <c r="T22" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="C35" s="8">
+        <v>2.4047999999999998</v>
+      </c>
+      <c r="D35" s="8">
+        <f>IFERROR(C32/C35,"")</f>
+        <v>39.384896872920827</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="4" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N23" s="4" t="e">
-        <f>_xlfn.STDEV.S(BenchmarkTable[[#This Row],[Rep 1]:[Promedio (s)]])</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="O23" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4">
-        <f>M20</f>
-        <v>18.732900000000001</v>
-      </c>
-      <c r="R23" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="S23" s="4">
-        <v>6</v>
-      </c>
-      <c r="T23" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
+      <c r="C36" s="6">
+        <v>28.4453</v>
+      </c>
+      <c r="D36" s="6">
+        <f>IFERROR(C32/C36,"")</f>
+        <v>3.3296467254695856</v>
+      </c>
+      <c r="K36" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="F20:J20"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
